--- a/output/pdf_financials_xlsx/OEC.H.xlsx
+++ b/output/pdf_financials_xlsx/OEC.H.xlsx
@@ -1336,7 +1336,7 @@
         <v>-5.233889</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.502453</v>
+        <v>-0.502453</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-0.052923</v>
@@ -1652,7 +1652,7 @@
         <v>-5.233889</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.502453</v>
+        <v>-0.502453</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-0.052923</v>
@@ -1835,7 +1835,7 @@
         <v>-5.233889</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.502453</v>
+        <v>-0.502453</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-0.052923</v>
@@ -2095,7 +2095,7 @@
         <v>-5.233889</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.502453</v>
+        <v>-0.502453</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.052923</v>
@@ -2217,7 +2217,7 @@
         <v>-5.233484</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.502453</v>
+        <v>-0.502453</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.052923</v>
@@ -2375,7 +2375,7 @@
         <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -6183,52 +6183,52 @@
         <v>1.64676</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.64676</v>
+        <v>2.020864</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.161207</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.103085</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.116638</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.487967</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.514019</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.514019</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.514019</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.532213</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.532213</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.532213</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.978375</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.978375</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.978375</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>5.070579</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>5.620471</v>
       </c>
     </row>
     <row r="93">
@@ -7743,7 +7743,7 @@
         <v>0</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
@@ -10032,7 +10032,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10520,7 +10524,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10714,7 +10722,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -11242,7 +11254,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -15606,7 +15622,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -17616,7 +17636,11 @@
           <t>Reserves 2,161,207</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -29610,7 +29634,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -52827,7 +52855,7 @@
         <v>-5.233889</v>
       </c>
       <c r="P424" s="5" t="n">
-        <v>0.502453</v>
+        <v>-0.502453</v>
       </c>
       <c r="Q424" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OEC.H.xlsx
+++ b/output/pdf_financials_xlsx/OEC.H.xlsx
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.005402</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004134</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00013</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.205378</v>
+        <v>-3.21078</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.157448</v>
+        <v>-1.161582</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.329474</v>
+        <v>-0.329604</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.585725</v>
@@ -2184,13 +2184,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.205378</v>
+        <v>-3.21078</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.157448</v>
+        <v>-1.161582</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.329474</v>
+        <v>-0.329604</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.585725</v>
@@ -2513,52 +2513,52 @@
         <v>0.010847</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.010847</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002455</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.162418</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.039095</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.015976</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.025186</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.002971</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.019668</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.058421</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.010117</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.040324</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.503525</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.03971</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.008207000000000001</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.007852</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.196983</v>
       </c>
     </row>
     <row r="35">
@@ -2635,52 +2635,52 @@
         <v>0.010847</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.010847</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002455</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.162418</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.039095</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.205155</v>
+        <v>0.221131</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.02251</v>
+        <v>0.047696</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.002971</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.019668</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.058421</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.010117</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.040324</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.503525</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.03971</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.008207000000000001</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.007852</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.196983</v>
       </c>
     </row>
     <row r="37">
@@ -3367,37 +3367,37 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.042624</v>
+        <v>0.031777</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.03352</v>
+        <v>0.031065</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.162685</v>
+        <v>0.000267</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.064362</v>
+        <v>0.025267</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.016243</v>
+        <v>0.000267</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.050114</v>
+        <v>0.024928</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002971</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.064668</v>
+        <v>0.045</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.073421</v>
+        <v>0.015</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.010117</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.040324</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -57370,7 +57370,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E468" s="5" t="n">

--- a/output/pdf_financials_xlsx/OEC.H.xlsx
+++ b/output/pdf_financials_xlsx/OEC.H.xlsx
@@ -7261,16 +7261,16 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.001164</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.017938</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.015222</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.004605</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>0</v>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002957</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -7298,10 +7298,10 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000899</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002956</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002957</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -8755,10 +8755,10 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000899</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002956</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.889167</v>
+        <v>-0.892124</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.285629</v>
@@ -8816,10 +8816,10 @@
         <v>-0.637131</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.103785</v>
+        <v>-1.104684</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-1.483003</v>
+        <v>-1.485959</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.842294</v>
@@ -23536,7 +23536,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -25520,7 +25524,11 @@
           <t>Proceeds from shares issued for cash</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -27188,7 +27196,11 @@
           <t>Proceeds from shares issued for cash (Note 8)</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -38380,7 +38392,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -44396,7 +44412,11 @@
           <t>Agent’s warrants issued pursuant to private placement $</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E341" s="5" t="n">
         <v>0.02693</v>
       </c>
@@ -45446,7 +45466,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E351" s="5" t="n">
         <v>-0.002957</v>
       </c>
